--- a/docs/harness/wirelist/B-cabin-pinouts.xlsx
+++ b/docs/harness/wirelist/B-cabin-pinouts.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/B-cabin-pinouts.xlsx
+++ b/docs/harness/wirelist/B-cabin-pinouts.xlsx
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+          <t>splice sp_shield_b_wsr (SP-SHIELD-B-WSR)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/B-cabin-pinouts.xlsx
+++ b/docs/harness/wirelist/B-cabin-pinouts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="IX-WS-R inline to rear VRC (das" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BH-B (firewall bulkhead DRB102,'!$A$2:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BH-B (firewall bulkhead DRB102,'!$A$2:$D$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BH-B (firewall bulkhead DRB102,'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ECU-B (Link G4X plug B, centre '!$A$2:$D$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'ECU-B (Link G4X plug B, centre '!$1:$2</definedName>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -560,103 +560,167 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w32_c</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr"/>
+          <t>Fuel pressure signal</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B16</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>w_gnd_b_c21</t>
+        </is>
+      </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr"/>
+          <t>Gnd fuel press + VSS</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>w35_c</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
+          <t>Coolant press signal</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B23</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>w29_c</t>
+        </is>
+      </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
+          <t>Oil pressure signal</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>w_gnd_b_c19</t>
+        </is>
+      </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
+          <t>Gnd oil/clnt/temps</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>w124_c</t>
+        </is>
+      </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr"/>
+          <t>ETB motor +</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B18</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>w215_c</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+          <t>ETB motor -</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>w_shc_etbm</t>
+        </is>
+      </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
+          <t>ETB motor shield</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
@@ -668,19 +732,27 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>w204_c</t>
+        </is>
+      </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
+          <t>Charge temp signal</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
@@ -692,295 +764,335 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>w203_c</t>
+        </is>
+      </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+          <t>Oil temp signal</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B6</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>w_rev_feed_c</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_rev_gauge (GAUGE 15A splice)</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>w_rail_sw12_b_c_ac</t>
+        </is>
+      </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
+          <t>+12 V gearbox speed</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>w_vss_sig_c</t>
+        </is>
+      </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+          <t>Gearbox speed signal</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B29</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>w_shc_vss</t>
+        </is>
+      </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
+          <t>Gearbox speed shield</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>w205_c</t>
+        </is>
+      </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+          <t>Knock sensor signal</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>w12_c</t>
+        </is>
+      </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
+          <t>Knock sensor (-)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>w_shc_knock1</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
+          <t>Knock sensor shield</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>w_rev_feed_c</t>
+        </is>
+      </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr"/>
+          <t>Back-up sw +12 V in</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>splice sp_rev_gauge (GAUGE 15A splice)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>w_rev_sw_c</t>
+        </is>
+      </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
+          <t>Reverse sw +12 V out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>splice sp_rev_sw (SP-REV)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>w29_c</t>
+          <t>wc_h_bh_bc</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Oil pressure signal</t>
+          <t>CAN H to CAN-Lambda</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B15</t>
+          <t>splice sp_canh (CAN H join)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>w32_c</t>
+          <t>wc_l_bh_bc</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Fuel pressure signal</t>
+          <t>CAN L to CAN-Lambda</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B16</t>
+          <t>splice sp_canl (CAN L join)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>w35_c</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Coolant press signal</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B23</t>
+          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>w203_c</t>
-        </is>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Oil temp signal</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B6</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>w204_c</t>
+          <t>w_lam12_cp</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Charge temp signal</t>
+          <t>CAN-Lambda +12 V</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B7</t>
+          <t>FB-LOGIC pin BUS2-1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>w_rev_sw_c</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>splice sp_rev_sw (SP-REV)</t>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>w_gnd_b_c19</t>
-        </is>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Gnd oil/clnt/temps</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>w_gnd_b_c21</t>
-        </is>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Gnd fuel press + VSS</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
-        </is>
-      </c>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B32" s="8" t="inlineStr"/>
       <c r="C32" s="9" t="inlineStr">
@@ -992,7 +1104,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
@@ -1004,7 +1116,7 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B34" s="8" t="inlineStr"/>
       <c r="C34" s="9" t="inlineStr">
@@ -1016,7 +1128,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr">
@@ -1026,360 +1138,8 @@
       </c>
       <c r="D35" s="7" t="inlineStr"/>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>w205_c</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Knock sensor signal</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B9</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>w12_c</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Knock sensor (-)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>w_shc_knock1</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Knock sensor shield</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>w124_c</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>ETB motor +</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B18</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>w215_c</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>ETB motor -</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B26</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>w_shc_etbm</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ETB motor shield</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>w_vss_sig_c</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Gearbox speed signal</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash) pin B29</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>w_rail_sw12_b_c_ac</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>+12 V gearbox speed</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>w_shc_vss</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Gearbox speed shield</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>wc_h_bh_bc</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>CAN H to CAN-Lambda</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_canh (CAN H join)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>wc_l_bh_bc</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>CAN L to CAN-Lambda</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>splice sp_canl (CAN L join)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>cab_canbh_bc_sh</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>CAN-Lambda shield</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>w_lam12_cp</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>CAN-Lambda +12 V</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>FB-LOGIC pin BUS2-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>w_lamg_ac</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>CAN-Lambda ground</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr"/>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr"/>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="n">
-        <v>101</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr"/>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D55"/>
+  <autoFilter ref="A2:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1525,7 +1285,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 74</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 61</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1307,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 75</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 59</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1343,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 83</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 71</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1459,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 71</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 28</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1481,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 72</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 14</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1525,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 86</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 45</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1635,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 73</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 26</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1701,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 87</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 46</t>
         </is>
       </c>
     </row>
@@ -2007,7 +1767,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH) pin 89</t>
+          <t>BH-B (firewall bulkhead DRB102, RH) pin 68</t>
         </is>
       </c>
     </row>
